--- a/artfynd/A 29725-2021 artfynd.xlsx
+++ b/artfynd/A 29725-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113440371</v>
+        <v>113440427</v>
       </c>
       <c r="B2" t="n">
-        <v>55987</v>
+        <v>78121</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>752926</v>
+        <v>753084</v>
       </c>
       <c r="R2" t="n">
-        <v>7189952</v>
+        <v>7190056</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,7 +785,7 @@
         <v>113440447</v>
       </c>
       <c r="B3" t="n">
-        <v>81846</v>
+        <v>81862</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113440427</v>
+        <v>113440448</v>
       </c>
       <c r="B4" t="n">
-        <v>78105</v>
+        <v>81862</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>753084</v>
+        <v>753067</v>
       </c>
       <c r="R4" t="n">
-        <v>7190056</v>
+        <v>7190060</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113440446</v>
+        <v>113440371</v>
       </c>
       <c r="B5" t="n">
-        <v>81846</v>
+        <v>55987</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,25 +1008,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>102613</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>752797</v>
+        <v>752926</v>
       </c>
       <c r="R5" t="n">
-        <v>7189880</v>
+        <v>7189952</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113440448</v>
+        <v>113440446</v>
       </c>
       <c r="B6" t="n">
-        <v>81846</v>
+        <v>81862</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>753067</v>
+        <v>752797</v>
       </c>
       <c r="R6" t="n">
-        <v>7190060</v>
+        <v>7189880</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 29725-2021 artfynd.xlsx
+++ b/artfynd/A 29725-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113440427</v>
+        <v>113440446</v>
       </c>
       <c r="B2" t="n">
-        <v>78121</v>
+        <v>81862</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>753084</v>
+        <v>752797</v>
       </c>
       <c r="R2" t="n">
-        <v>7190056</v>
+        <v>7189880</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113440447</v>
+        <v>113440371</v>
       </c>
       <c r="B3" t="n">
-        <v>81862</v>
+        <v>55987</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>102613</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>753034</v>
+        <v>752926</v>
       </c>
       <c r="R3" t="n">
-        <v>7190027</v>
+        <v>7189952</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113440448</v>
+        <v>113440447</v>
       </c>
       <c r="B4" t="n">
         <v>81862</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>753067</v>
+        <v>753034</v>
       </c>
       <c r="R4" t="n">
-        <v>7190060</v>
+        <v>7190027</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113440371</v>
+        <v>113440427</v>
       </c>
       <c r="B5" t="n">
-        <v>55987</v>
+        <v>78121</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,25 +1008,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>752926</v>
+        <v>753084</v>
       </c>
       <c r="R5" t="n">
-        <v>7189952</v>
+        <v>7190056</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113440446</v>
+        <v>113440448</v>
       </c>
       <c r="B6" t="n">
         <v>81862</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>752797</v>
+        <v>753067</v>
       </c>
       <c r="R6" t="n">
-        <v>7189880</v>
+        <v>7190060</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 29725-2021 artfynd.xlsx
+++ b/artfynd/A 29725-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113440446</v>
+        <v>113440427</v>
       </c>
       <c r="B2" t="n">
-        <v>81862</v>
+        <v>78133</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>752797</v>
+        <v>753084</v>
       </c>
       <c r="R2" t="n">
-        <v>7189880</v>
+        <v>7190056</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113440371</v>
+        <v>113440447</v>
       </c>
       <c r="B3" t="n">
-        <v>55987</v>
+        <v>81874</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102613</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>752926</v>
+        <v>753034</v>
       </c>
       <c r="R3" t="n">
-        <v>7189952</v>
+        <v>7190027</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113440447</v>
+        <v>113440371</v>
       </c>
       <c r="B4" t="n">
-        <v>81862</v>
+        <v>55988</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>102613</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>753034</v>
+        <v>752926</v>
       </c>
       <c r="R4" t="n">
-        <v>7190027</v>
+        <v>7189952</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113440427</v>
+        <v>113440448</v>
       </c>
       <c r="B5" t="n">
-        <v>78121</v>
+        <v>81874</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>753084</v>
+        <v>753067</v>
       </c>
       <c r="R5" t="n">
-        <v>7190056</v>
+        <v>7190060</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113440448</v>
+        <v>113440446</v>
       </c>
       <c r="B6" t="n">
-        <v>81862</v>
+        <v>81874</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>753067</v>
+        <v>752797</v>
       </c>
       <c r="R6" t="n">
-        <v>7190060</v>
+        <v>7189880</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 29725-2021 artfynd.xlsx
+++ b/artfynd/A 29725-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113440427</v>
+        <v>113440447</v>
       </c>
       <c r="B2" t="n">
-        <v>78133</v>
+        <v>81874</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>753084</v>
+        <v>753034</v>
       </c>
       <c r="R2" t="n">
-        <v>7190056</v>
+        <v>7190027</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113440447</v>
+        <v>113440371</v>
       </c>
       <c r="B3" t="n">
-        <v>81874</v>
+        <v>55988</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>102613</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>753034</v>
+        <v>752926</v>
       </c>
       <c r="R3" t="n">
-        <v>7190027</v>
+        <v>7189952</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113440371</v>
+        <v>113440427</v>
       </c>
       <c r="B4" t="n">
-        <v>55988</v>
+        <v>78133</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>752926</v>
+        <v>753084</v>
       </c>
       <c r="R4" t="n">
-        <v>7189952</v>
+        <v>7190056</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113440448</v>
+        <v>113440446</v>
       </c>
       <c r="B5" t="n">
         <v>81874</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>753067</v>
+        <v>752797</v>
       </c>
       <c r="R5" t="n">
-        <v>7190060</v>
+        <v>7189880</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113440446</v>
+        <v>113440448</v>
       </c>
       <c r="B6" t="n">
         <v>81874</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>752797</v>
+        <v>753067</v>
       </c>
       <c r="R6" t="n">
-        <v>7189880</v>
+        <v>7190060</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 29725-2021 artfynd.xlsx
+++ b/artfynd/A 29725-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113440447</v>
+        <v>113440427</v>
       </c>
       <c r="B2" t="n">
-        <v>81874</v>
+        <v>78155</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>753034</v>
+        <v>753084</v>
       </c>
       <c r="R2" t="n">
-        <v>7190027</v>
+        <v>7190056</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113440371</v>
+        <v>113440447</v>
       </c>
       <c r="B3" t="n">
-        <v>55988</v>
+        <v>81896</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102613</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>752926</v>
+        <v>753034</v>
       </c>
       <c r="R3" t="n">
-        <v>7189952</v>
+        <v>7190027</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113440427</v>
+        <v>113440371</v>
       </c>
       <c r="B4" t="n">
-        <v>78133</v>
+        <v>55988</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>753084</v>
+        <v>752926</v>
       </c>
       <c r="R4" t="n">
-        <v>7190056</v>
+        <v>7189952</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113440446</v>
+        <v>113440448</v>
       </c>
       <c r="B5" t="n">
-        <v>81874</v>
+        <v>81896</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>752797</v>
+        <v>753067</v>
       </c>
       <c r="R5" t="n">
-        <v>7189880</v>
+        <v>7190060</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113440448</v>
+        <v>113440446</v>
       </c>
       <c r="B6" t="n">
-        <v>81874</v>
+        <v>81896</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>753067</v>
+        <v>752797</v>
       </c>
       <c r="R6" t="n">
-        <v>7190060</v>
+        <v>7189880</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 29725-2021 artfynd.xlsx
+++ b/artfynd/A 29725-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113440427</v>
       </c>
       <c r="B2" t="n">
-        <v>78155</v>
+        <v>78158</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113440447</v>
+        <v>113440371</v>
       </c>
       <c r="B3" t="n">
-        <v>81896</v>
+        <v>55991</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>102613</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>753034</v>
+        <v>752926</v>
       </c>
       <c r="R3" t="n">
-        <v>7190027</v>
+        <v>7189952</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113440371</v>
+        <v>113440448</v>
       </c>
       <c r="B4" t="n">
-        <v>55988</v>
+        <v>81900</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102613</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>752926</v>
+        <v>753067</v>
       </c>
       <c r="R4" t="n">
-        <v>7189952</v>
+        <v>7190060</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113440448</v>
+        <v>113440447</v>
       </c>
       <c r="B5" t="n">
-        <v>81896</v>
+        <v>81900</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>753067</v>
+        <v>753034</v>
       </c>
       <c r="R5" t="n">
-        <v>7190060</v>
+        <v>7190027</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1106,7 @@
         <v>113440446</v>
       </c>
       <c r="B6" t="n">
-        <v>81896</v>
+        <v>81900</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 29725-2021 artfynd.xlsx
+++ b/artfynd/A 29725-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113440427</v>
+        <v>113440448</v>
       </c>
       <c r="B2" t="n">
-        <v>78158</v>
+        <v>81906</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>753084</v>
+        <v>753067</v>
       </c>
       <c r="R2" t="n">
-        <v>7190056</v>
+        <v>7190060</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113440371</v>
+        <v>113440427</v>
       </c>
       <c r="B3" t="n">
-        <v>55991</v>
+        <v>78164</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>752926</v>
+        <v>753084</v>
       </c>
       <c r="R3" t="n">
-        <v>7189952</v>
+        <v>7190056</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113440448</v>
+        <v>113440446</v>
       </c>
       <c r="B4" t="n">
-        <v>81900</v>
+        <v>81906</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>753067</v>
+        <v>752797</v>
       </c>
       <c r="R4" t="n">
-        <v>7190060</v>
+        <v>7189880</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
         <v>113440447</v>
       </c>
       <c r="B5" t="n">
-        <v>81900</v>
+        <v>81906</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113440446</v>
+        <v>113440371</v>
       </c>
       <c r="B6" t="n">
-        <v>81900</v>
+        <v>55995</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,25 +1115,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>102613</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>752797</v>
+        <v>752926</v>
       </c>
       <c r="R6" t="n">
-        <v>7189880</v>
+        <v>7189952</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 29725-2021 artfynd.xlsx
+++ b/artfynd/A 29725-2021 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113440427</v>
+        <v>113440447</v>
       </c>
       <c r="B3" t="n">
-        <v>78164</v>
+        <v>81906</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>753084</v>
+        <v>753034</v>
       </c>
       <c r="R3" t="n">
-        <v>7190056</v>
+        <v>7190027</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113440446</v>
+        <v>113440427</v>
       </c>
       <c r="B4" t="n">
-        <v>81906</v>
+        <v>78164</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>752797</v>
+        <v>753084</v>
       </c>
       <c r="R4" t="n">
-        <v>7189880</v>
+        <v>7190056</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113440447</v>
+        <v>113440446</v>
       </c>
       <c r="B5" t="n">
         <v>81906</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>753034</v>
+        <v>752797</v>
       </c>
       <c r="R5" t="n">
-        <v>7190027</v>
+        <v>7189880</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 29725-2021 artfynd.xlsx
+++ b/artfynd/A 29725-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113440448</v>
       </c>
       <c r="B2" t="n">
-        <v>81906</v>
+        <v>81913</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113440447</v>
+        <v>113440371</v>
       </c>
       <c r="B3" t="n">
-        <v>81906</v>
+        <v>56002</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>102613</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>753034</v>
+        <v>752926</v>
       </c>
       <c r="R3" t="n">
-        <v>7190027</v>
+        <v>7189952</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113440427</v>
+        <v>113440446</v>
       </c>
       <c r="B4" t="n">
-        <v>78164</v>
+        <v>81913</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>753084</v>
+        <v>752797</v>
       </c>
       <c r="R4" t="n">
-        <v>7190056</v>
+        <v>7189880</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113440446</v>
+        <v>113440447</v>
       </c>
       <c r="B5" t="n">
-        <v>81906</v>
+        <v>81913</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>752797</v>
+        <v>753034</v>
       </c>
       <c r="R5" t="n">
-        <v>7189880</v>
+        <v>7190027</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113440371</v>
+        <v>113440427</v>
       </c>
       <c r="B6" t="n">
-        <v>55995</v>
+        <v>78171</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,25 +1115,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>752926</v>
+        <v>753084</v>
       </c>
       <c r="R6" t="n">
-        <v>7189952</v>
+        <v>7190056</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 29725-2021 artfynd.xlsx
+++ b/artfynd/A 29725-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113440448</v>
+        <v>113440447</v>
       </c>
       <c r="B2" t="n">
-        <v>81913</v>
+        <v>81916</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>753067</v>
+        <v>753034</v>
       </c>
       <c r="R2" t="n">
-        <v>7190060</v>
+        <v>7190027</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113440371</v>
+        <v>113440448</v>
       </c>
       <c r="B3" t="n">
-        <v>56002</v>
+        <v>81916</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102613</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>752926</v>
+        <v>753067</v>
       </c>
       <c r="R3" t="n">
-        <v>7189952</v>
+        <v>7190060</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113440446</v>
+        <v>113440427</v>
       </c>
       <c r="B4" t="n">
-        <v>81913</v>
+        <v>78173</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>752797</v>
+        <v>753084</v>
       </c>
       <c r="R4" t="n">
-        <v>7189880</v>
+        <v>7190056</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113440447</v>
+        <v>113440371</v>
       </c>
       <c r="B5" t="n">
-        <v>81913</v>
+        <v>56004</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,25 +1008,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>102613</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>753034</v>
+        <v>752926</v>
       </c>
       <c r="R5" t="n">
-        <v>7190027</v>
+        <v>7189952</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113440427</v>
+        <v>113440446</v>
       </c>
       <c r="B6" t="n">
-        <v>78171</v>
+        <v>81916</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>753084</v>
+        <v>752797</v>
       </c>
       <c r="R6" t="n">
-        <v>7190056</v>
+        <v>7189880</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 29725-2021 artfynd.xlsx
+++ b/artfynd/A 29725-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113440447</v>
+        <v>113440427</v>
       </c>
       <c r="B2" t="n">
-        <v>81916</v>
+        <v>78201</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>753034</v>
+        <v>753084</v>
       </c>
       <c r="R2" t="n">
-        <v>7190027</v>
+        <v>7190056</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113440448</v>
+        <v>113440447</v>
       </c>
       <c r="B3" t="n">
-        <v>81916</v>
+        <v>81944</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>753067</v>
+        <v>753034</v>
       </c>
       <c r="R3" t="n">
-        <v>7190060</v>
+        <v>7190027</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113440427</v>
+        <v>113440446</v>
       </c>
       <c r="B4" t="n">
-        <v>78173</v>
+        <v>81944</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>753084</v>
+        <v>752797</v>
       </c>
       <c r="R4" t="n">
-        <v>7190056</v>
+        <v>7189880</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
         <v>113440371</v>
       </c>
       <c r="B5" t="n">
-        <v>56004</v>
+        <v>56032</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113440446</v>
+        <v>113440448</v>
       </c>
       <c r="B6" t="n">
-        <v>81916</v>
+        <v>81944</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>752797</v>
+        <v>753067</v>
       </c>
       <c r="R6" t="n">
-        <v>7189880</v>
+        <v>7190060</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 29725-2021 artfynd.xlsx
+++ b/artfynd/A 29725-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113440427</v>
+        <v>113440446</v>
       </c>
       <c r="B2" t="n">
-        <v>78201</v>
+        <v>81944</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>753084</v>
+        <v>752797</v>
       </c>
       <c r="R2" t="n">
-        <v>7190056</v>
+        <v>7189880</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113440447</v>
+        <v>113440371</v>
       </c>
       <c r="B3" t="n">
-        <v>81944</v>
+        <v>56032</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>102613</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>753034</v>
+        <v>752926</v>
       </c>
       <c r="R3" t="n">
-        <v>7190027</v>
+        <v>7189952</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113440446</v>
+        <v>113440448</v>
       </c>
       <c r="B4" t="n">
         <v>81944</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>752797</v>
+        <v>753067</v>
       </c>
       <c r="R4" t="n">
-        <v>7189880</v>
+        <v>7190060</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113440371</v>
+        <v>113440427</v>
       </c>
       <c r="B5" t="n">
-        <v>56032</v>
+        <v>78201</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,25 +1008,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>752926</v>
+        <v>753084</v>
       </c>
       <c r="R5" t="n">
-        <v>7189952</v>
+        <v>7190056</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113440448</v>
+        <v>113440447</v>
       </c>
       <c r="B6" t="n">
         <v>81944</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>753067</v>
+        <v>753034</v>
       </c>
       <c r="R6" t="n">
-        <v>7190060</v>
+        <v>7190027</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 29725-2021 artfynd.xlsx
+++ b/artfynd/A 29725-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113440446</v>
+        <v>113440447</v>
       </c>
       <c r="B2" t="n">
         <v>81944</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>752797</v>
+        <v>753034</v>
       </c>
       <c r="R2" t="n">
-        <v>7189880</v>
+        <v>7190027</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113440371</v>
+        <v>113440427</v>
       </c>
       <c r="B3" t="n">
-        <v>56032</v>
+        <v>78201</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>752926</v>
+        <v>753084</v>
       </c>
       <c r="R3" t="n">
-        <v>7189952</v>
+        <v>7190056</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113440448</v>
+        <v>113440446</v>
       </c>
       <c r="B4" t="n">
         <v>81944</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>753067</v>
+        <v>752797</v>
       </c>
       <c r="R4" t="n">
-        <v>7190060</v>
+        <v>7189880</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113440427</v>
+        <v>113440448</v>
       </c>
       <c r="B5" t="n">
-        <v>78201</v>
+        <v>81944</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>753084</v>
+        <v>753067</v>
       </c>
       <c r="R5" t="n">
-        <v>7190056</v>
+        <v>7190060</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113440447</v>
+        <v>113440371</v>
       </c>
       <c r="B6" t="n">
-        <v>81944</v>
+        <v>56032</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,25 +1115,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>102613</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>753034</v>
+        <v>752926</v>
       </c>
       <c r="R6" t="n">
-        <v>7190027</v>
+        <v>7189952</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 29725-2021 artfynd.xlsx
+++ b/artfynd/A 29725-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
